--- a/output/pdf_financials_xlsx/YGR.xlsx
+++ b/output/pdf_financials_xlsx/YGR.xlsx
@@ -934,10 +934,10 @@
         <v>0</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>0.972706</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>1.057597</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0</v>
@@ -38362,7 +38362,11 @@
           <t>Royalty expense</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -38379,10 +38383,10 @@
         </is>
       </c>
       <c r="H295" s="5" t="n">
-        <v>-0.972706</v>
+        <v>0.972706</v>
       </c>
       <c r="I295" s="5" t="n">
-        <v>-1.057597</v>
+        <v>1.057597</v>
       </c>
       <c r="J295" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/YGR.xlsx
+++ b/output/pdf_financials_xlsx/YGR.xlsx
@@ -7496,10 +7496,8 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0.078776</v>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
@@ -31013,7 +31011,11 @@
           <t>Proceeds on disposition of property and equipment</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E220" s="5" t="n">
         <v>0.078776</v>
       </c>
